--- a/backend/examples/excel/汽车产业链示例.xlsx
+++ b/backend/examples/excel/汽车产业链示例.xlsx
@@ -95,7 +95,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">导入：python examples/excel/build_from_sheets.py examples/excel/汽车产业链示例.xlsx --competition &lt;比赛id&gt; --dry-run</t>
+          <t xml:space="preserve">导入：python examples/excel/build_from_sheets.py examples/excel/汽车产业链示例.xlsx --create-competition</t>
         </is>
       </c>
     </row>
@@ -109,17 +109,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">color</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
     </row>
@@ -184,27 +184,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">节点名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node_type</t>
+          <t xml:space="preserve">节点类型</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">所属区域</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">x</t>
+          <t xml:space="preserve">X坐标</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">y</t>
+          <t xml:space="preserve">Y坐标</t>
         </is>
       </c>
     </row>
@@ -402,22 +402,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_node</t>
+          <t xml:space="preserve">起点节点</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">to_node</t>
+          <t xml:space="preserve">终点节点</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">distance</t>
+          <t xml:space="preserve">距离(公里)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">path_type</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
     </row>
@@ -651,12 +651,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">燃料名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">price_per_liter</t>
+          <t xml:space="preserve">每升单价</t>
         </is>
       </c>
     </row>
@@ -694,27 +694,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">原料名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">origin</t>
+          <t xml:space="preserve">产地</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_emission_coefficient</t>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">类型</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node_prices</t>
+          <t xml:space="preserve">地点价</t>
         </is>
       </c>
     </row>
@@ -863,27 +863,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">科技名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tier</t>
+          <t xml:space="preserve">层级</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">research_cost</t>
+          <t xml:space="preserve">研发费用</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prerequisites</t>
+          <t xml:space="preserve">前置科技</t>
         </is>
       </c>
     </row>
@@ -982,22 +982,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">生产线名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">labor_count</t>
+          <t xml:space="preserve">用工人数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_per_year</t>
+          <t xml:space="preserve">年产能</t>
         </is>
       </c>
     </row>
@@ -1091,52 +1091,52 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">基建名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">footprint</t>
+          <t xml:space="preserve">占地面积</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">activation_price</t>
+          <t xml:space="preserve">启用费用</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">employment_rate_bonus</t>
+          <t xml:space="preserve">就业率加成</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">population_bonus</t>
+          <t xml:space="preserve">人口加成</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">high_quality_population_bonus</t>
+          <t xml:space="preserve">高素质人口加成</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">happiness_index_bonus</t>
+          <t xml:space="preserve">幸福度加成</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">per_capita_income_bonus</t>
+          <t xml:space="preserve">人均收益加成</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_reduction_bonus</t>
+          <t xml:space="preserve">减碳加成</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">仓库名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">仓库种类</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacity</t>
+          <t xml:space="preserve">容量</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">零件名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">materials</t>
+          <t xml:space="preserve">原料配比</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tech</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">比赛名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图背景图地址</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">背景图宽</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">背景图高</t>
         </is>
       </c>
     </row>
@@ -1492,17 +1507,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">产品名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">parts</t>
+          <t xml:space="preserve">零件配比</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tech</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
     </row>
@@ -1567,37 +1582,37 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">载具名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">path_types</t>
+          <t xml:space="preserve">可通行路径类型</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel_consumption_per_km</t>
+          <t xml:space="preserve">每公里油耗</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_cargo</t>
+          <t xml:space="preserve">载货量</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_emission</t>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
     </row>
@@ -1821,22 +1836,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">区域名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">product</t>
+          <t xml:space="preserve">产品名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantity</t>
+          <t xml:space="preserve">需求量</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">备注</t>
         </is>
       </c>
     </row>
@@ -1930,22 +1945,32 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">区域名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">company</t>
+          <t xml:space="preserve">公司名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_key</t>
+          <t xml:space="preserve">字段键</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">display_name</t>
+          <t xml:space="preserve">卡片标题</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分区标记</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卡片ID</t>
         </is>
       </c>
     </row>
@@ -2157,22 +2182,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">类型标识</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">合同名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">脚本路径</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参与方</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">输入项定义</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果定义</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前置检查</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否启用</t>
         </is>
       </c>
     </row>
@@ -2252,27 +2302,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contract_type</t>
+          <t xml:space="preserve">合同类型标识</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">合同名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">parties</t>
+          <t xml:space="preserve">参与方</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inputs</t>
+          <t xml:space="preserve">输入项</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">状态</t>
         </is>
       </c>
     </row>
@@ -2367,17 +2417,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">标题</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">content</t>
+          <t xml:space="preserve">正文</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">to_all</t>
+          <t xml:space="preserve">是否发给全体</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定收件人</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发布者</t>
         </is>
       </c>
     </row>
@@ -2442,42 +2502,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">username</t>
+          <t xml:space="preserve">用户名</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">角色</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">display_name</t>
+          <t xml:space="preserve">显示名</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">company_scopes</t>
+          <t xml:space="preserve">公司管理范围</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">view_company_scopes</t>
+          <t xml:space="preserve">查看范围</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contract_view_company_scopes</t>
+          <t xml:space="preserve">合同查看范围</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stock_company_scopes</t>
+          <t xml:space="preserve">股票范围</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">permissions</t>
+          <t xml:space="preserve">权限键</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否启用</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2689,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">year</t>
+          <t xml:space="preserve">年份</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">状态</t>
         </is>
       </c>
     </row>
@@ -2655,17 +2720,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">code</t>
+          <t xml:space="preserve">编码</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">产业名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">图标</t>
         </is>
       </c>
     </row>
@@ -2730,67 +2800,67 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry_type</t>
+          <t xml:space="preserve">所属产业</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">字段名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_key</t>
+          <t xml:space="preserve">字段键</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_type</t>
+          <t xml:space="preserve">字段类型</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">default_value</t>
+          <t xml:space="preserve">默认值</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">is_calculated</t>
+          <t xml:space="preserve">是否计算字段</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">graph</t>
+          <t xml:space="preserve">计算图</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_enabled</t>
+          <t xml:space="preserve">启用财年定时器</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_trigger</t>
+          <t xml:space="preserve">定时器时机</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_value</t>
+          <t xml:space="preserve">定时器写入值</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sort_order</t>
+          <t xml:space="preserve">排序</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t xml:space="preserve">visible</t>
+          <t xml:space="preserve">是否展示</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t xml:space="preserve">config</t>
+          <t xml:space="preserve">类型配置</t>
         </is>
       </c>
     </row>
@@ -4262,12 +4332,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">区域名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
     </row>
@@ -4317,47 +4387,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">公司名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry_type</t>
+          <t xml:space="preserve">所属产业</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">所属区域</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">状态</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">location</t>
+          <t xml:space="preserve">所在地</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">cash</t>
+          <t xml:space="preserve">现金</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank_deposit</t>
+          <t xml:space="preserve">银行存款</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">quota</t>
+          <t xml:space="preserve">许可配额</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inventory</t>
+          <t xml:space="preserve">库存台账</t>
         </is>
       </c>
     </row>
@@ -4794,17 +4864,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">company</t>
+          <t xml:space="preserve">公司名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_key</t>
+          <t xml:space="preserve">字段键</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">值</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4886,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">last_deal</t>
+          <t xml:space="preserve">最近业务摘要</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4833,7 +4903,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ledger</t>
+          <t xml:space="preserve">业务台账</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4850,7 +4920,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ledger</t>
+          <t xml:space="preserve">业务台账</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4869,17 +4939,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">color</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
     </row>

--- a/backend/examples/excel/汽车产业链示例.xlsx
+++ b/backend/examples/excel/汽车产业链示例.xlsx
@@ -8,27 +8,21 @@
     <sheet name="产业类型" sheetId="4" r:id="rId4"/>
     <sheet name="产业字段" sheetId="5" r:id="rId5"/>
     <sheet name="区域" sheetId="6" r:id="rId6"/>
-    <sheet name="公司" sheetId="7" r:id="rId7"/>
-    <sheet name="公司字段值" sheetId="8" r:id="rId8"/>
-    <sheet name="地图节点类型" sheetId="9" r:id="rId9"/>
-    <sheet name="路径类型" sheetId="10" r:id="rId10"/>
-    <sheet name="地图节点" sheetId="11" r:id="rId11"/>
-    <sheet name="地图连线" sheetId="12" r:id="rId12"/>
-    <sheet name="燃料" sheetId="13" r:id="rId13"/>
-    <sheet name="原料" sheetId="14" r:id="rId14"/>
-    <sheet name="科技" sheetId="15" r:id="rId15"/>
-    <sheet name="生产线" sheetId="16" r:id="rId16"/>
-    <sheet name="基建" sheetId="17" r:id="rId17"/>
-    <sheet name="仓库" sheetId="18" r:id="rId18"/>
-    <sheet name="零件" sheetId="19" r:id="rId19"/>
-    <sheet name="产品" sheetId="20" r:id="rId20"/>
-    <sheet name="载具" sheetId="21" r:id="rId21"/>
-    <sheet name="消费者需求" sheetId="22" r:id="rId22"/>
-    <sheet name="区域总览卡片" sheetId="23" r:id="rId23"/>
-    <sheet name="合同类型" sheetId="24" r:id="rId24"/>
-    <sheet name="合同实例" sheetId="25" r:id="rId25"/>
-    <sheet name="消息" sheetId="26" r:id="rId26"/>
-    <sheet name="账号" sheetId="27" r:id="rId27"/>
+    <sheet name="地图节点类型" sheetId="7" r:id="rId7"/>
+    <sheet name="路径类型" sheetId="8" r:id="rId8"/>
+    <sheet name="地图节点" sheetId="9" r:id="rId9"/>
+    <sheet name="地图连线" sheetId="10" r:id="rId10"/>
+    <sheet name="燃料" sheetId="11" r:id="rId11"/>
+    <sheet name="原料" sheetId="12" r:id="rId12"/>
+    <sheet name="科技" sheetId="13" r:id="rId13"/>
+    <sheet name="生产线" sheetId="14" r:id="rId14"/>
+    <sheet name="基建" sheetId="15" r:id="rId15"/>
+    <sheet name="仓库" sheetId="16" r:id="rId16"/>
+    <sheet name="零件" sheetId="17" r:id="rId17"/>
+    <sheet name="产品" sheetId="18" r:id="rId18"/>
+    <sheet name="载具" sheetId="19" r:id="rId19"/>
+    <sheet name="消费者需求" sheetId="20" r:id="rId20"/>
+    <sheet name="合同类型" sheetId="21" r:id="rId21"/>
   </sheets>
 </workbook>
 </file>
@@ -67,33 +61,56 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">汽车产业链测试赛 · 表格建包示例</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">与代码建包脚本 examples/competitions/auto_chain_competition.py 描述同一场比赛。</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">汽车产业链 · 比赛框架表格示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">股票系统不在本规范内：本示例不产出任何股票 / 资金账户 / 股票参数。</t>
+          <t xml:space="preserve">本表格只描述「比赛框架」：产业口径、地图与物流、物资与产能、需求、合同类型。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">用法：python examples/excel/build_from_sheets.py examples/excel/汽车产业链示例.xlsx --inspect</t>
+          <t xml:space="preserve">参赛主体与运行期内容不在表格里（公司、公司字段值、账号、区域总览卡片、合同实例、消息）：</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 界面维护：公司管理 / 账号管理 / 区域总览 / 合同管理 / 消息中心；</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 或一次建齐（框架 + 主体）：python manage.py build_competition examples/competitions/auto_chain_competition.py --competition &lt;比赛id&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">股票系统同样不在本规范内：本示例不产出任何股票 / 资金账户 / 股票参数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用法：python examples/excel/build_from_sheets.py examples/excel/汽车产业链示例.xlsx --inspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t xml:space="preserve">导入：python examples/excel/build_from_sheets.py examples/excel/汽车产业链示例.xlsx --create-competition</t>
         </is>
@@ -109,68 +126,242 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型名称</t>
+          <t xml:space="preserve">起点节点</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">终点节点</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">颜色</t>
+          <t xml:space="preserve">距离(公里)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">白云鄂博矿区</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上游集运站</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>120</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t xml:space="preserve">公路</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通用公路运输</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#94a3b8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">铁路</t>
+          <t xml:space="preserve">戈壁铝土矿区</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">大宗干线运输</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#a16207</t>
+          <t xml:space="preserve">上游集运站</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>80</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公路</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">橡胶硅砂基地</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上游集运站</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>160</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公路</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上游集运站</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中部智造园</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>420</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">铁路</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中部智造园</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上游集运站</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>430</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公路</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上游集运站</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东部车都港</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>1200</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t xml:space="preserve">内河航运</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">港口水运</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#0369a1</t>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中部智造园</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中原铁路货场</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>60</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公路</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中原铁路货场</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东部车都港</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>400</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">铁路</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中部智造园</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东部车都港</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>380</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公路</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东部车都港</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中部智造园</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>390</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">铁路</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东部车都港</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">车都展销中心</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>60</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公路</t>
         </is>
       </c>
     </row>
@@ -184,212 +375,37 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点名称</t>
+          <t xml:space="preserve">燃料名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点类型</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">所属区域</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X坐标</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y坐标</t>
+          <t xml:space="preserve">每升单价</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">白云鄂博矿区</t>
+          <t xml:space="preserve">柴油</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿区</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>140</v>
-      </c>
-      <c r="E2">
-        <v>120</v>
+          <t xml:space="preserve">7.6</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">戈壁铝土矿区</t>
+          <t xml:space="preserve">电力</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿区</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>140</v>
-      </c>
-      <c r="E3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">橡胶硅砂基地</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">矿区</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>140</v>
-      </c>
-      <c r="E4">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游集运站</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">物流枢纽</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>360</v>
-      </c>
-      <c r="E5">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造园</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">产业园区</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造区</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>620</v>
-      </c>
-      <c r="E6">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中原铁路货场</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">物流枢纽</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造区</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>620</v>
-      </c>
-      <c r="E7">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都港</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">物流枢纽</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>900</v>
-      </c>
-      <c r="E8">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">车都展销中心</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">销售中心</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>1040</v>
-      </c>
-      <c r="E9">
-        <v>380</v>
+          <t xml:space="preserve">0.8</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -402,242 +418,162 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">起点节点</t>
+          <t xml:space="preserve">原料名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">终点节点</t>
+          <t xml:space="preserve">产地</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">距离(公里)</t>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">类型</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地点价</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">锂矿石</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">白云鄂博矿区</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游集运站</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>120</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.52</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">公路</t>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白云鄂博矿区:180; 上游集运站:195; 中部智造园:215; 东部车都港:240</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t xml:space="preserve">铝土矿</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t xml:space="preserve">戈壁铝土矿区</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游集运站</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>80</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.41</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">公路</t>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">戈壁铝土矿区:165; 上游集运站:180; 中部智造园:205; 东部车都港:230</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">橡胶硅砂基地</t>
+          <t xml:space="preserve">铁矿石</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">上游集运站</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>160</v>
+          <t xml:space="preserve">白云鄂博矿区</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.48</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">公路</t>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白云鄂博矿区:120; 上游集运站:132; 中部智造园:150; 东部车都港:168</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">上游集运站</t>
+          <t xml:space="preserve">天然橡胶</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">中部智造园</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>420</v>
+          <t xml:space="preserve">橡胶硅砂基地</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.33</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">铁路</t>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">橡胶硅砂基地:90; 上游集运站:98; 中部智造园:110; 东部车都港:126</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">中部智造园</t>
+          <t xml:space="preserve">石英砂</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">上游集运站</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>430</v>
+          <t xml:space="preserve">橡胶硅砂基地</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.22</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">公路</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游集运站</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都港</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>1200</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内河航运</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造园</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中原铁路货场</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>60</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公路</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中原铁路货场</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都港</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>400</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">铁路</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造园</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都港</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>380</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公路</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都港</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造园</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>390</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">铁路</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都港</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">车都展销中心</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>60</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公路</t>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">橡胶硅砂基地:60; 上游集运站:66; 中部智造园:75; 东部车都港:86</t>
         </is>
       </c>
     </row>
@@ -651,36 +587,112 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料名称</t>
+          <t xml:space="preserve">科技名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">每升单价</t>
+          <t xml:space="preserve">层级</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">研发费用</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说明</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前置科技</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">柴油</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.6</t>
+          <t xml:space="preserve">电池成组技术</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">解锁动力电池包</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">电力</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.8</t>
+          <t xml:space="preserve">电驱系统集成</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">解锁驱动电机</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轻量化车身工艺</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">解锁铝合金车身</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">整车平台化</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">解锁整车产品</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">电池成组技术; 电驱系统集成</t>
         </is>
       </c>
     </row>
@@ -694,162 +706,102 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料名称</t>
+          <t xml:space="preserve">生产线名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">产地</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">碳排系数</t>
+          <t xml:space="preserve">用工人数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">地点价</t>
+          <t xml:space="preserve">年产能</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">锂矿石</t>
+          <t xml:space="preserve">电芯产线</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">白云鄂博矿区</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.52</t>
-        </is>
+          <t xml:space="preserve">2400000</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NORMAL</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白云鄂博矿区:180; 上游集运站:195; 中部智造园:215; 东部车都港:240</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">铝土矿</t>
+          <t xml:space="preserve">电驱总装线</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">戈壁铝土矿区</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.41</t>
-        </is>
+          <t xml:space="preserve">1600000</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>80</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NORMAL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">戈壁铝土矿区:165; 上游集运站:180; 中部智造园:205; 东部车都港:230</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">铁矿石</t>
+          <t xml:space="preserve">车身冲压线</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">白云鄂博矿区</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.48</t>
-        </is>
+          <t xml:space="preserve">1200000</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>60</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NORMAL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白云鄂博矿区:120; 上游集运站:132; 中部智造园:150; 东部车都港:168</t>
+          <t xml:space="preserve">9000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">天然橡胶</t>
+          <t xml:space="preserve">整车总装线</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">橡胶硅砂基地</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.33</t>
-        </is>
+          <t xml:space="preserve">3600000</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NORMAL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">橡胶硅砂基地:90; 上游集运站:98; 中部智造园:110; 东部车都港:126</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">石英砂</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">橡胶硅砂基地</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.22</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NORMAL</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">橡胶硅砂基地:60; 上游集运站:66; 中部智造园:75; 东部车都港:86</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
     </row>
@@ -863,112 +815,142 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技名称</t>
+          <t xml:space="preserve">基建名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">层级</t>
+          <t xml:space="preserve">占地面积</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">研发费用</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">启用费用</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">前置科技</t>
+          <t xml:space="preserve">就业率加成</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人口加成</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高素质人口加成</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幸福度加成</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人均收益加成</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">减碳加成</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">电池成组技术</t>
+          <t xml:space="preserve">智能充电站</t>
         </is>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80000</t>
+          <t xml:space="preserve">600000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">解锁动力电池包</t>
+          <t xml:space="preserve">30000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.01</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">电驱系统集成</t>
+          <t xml:space="preserve">汽车试验场</t>
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60000</t>
+          <t xml:space="preserve">1500000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">解锁驱动电机</t>
+          <t xml:space="preserve">80000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.03</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">轻量化车身工艺</t>
+          <t xml:space="preserve">光伏电站</t>
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t xml:space="preserve">1200000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t xml:space="preserve">50000</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">解锁铝合金车身</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">整车平台化</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200000</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">解锁整车产品</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">电池成组技术; 电驱系统集成</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.02</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.12</t>
         </is>
       </c>
     </row>
@@ -982,102 +964,110 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线名称</t>
+          <t xml:space="preserve">仓库名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t xml:space="preserve">仓库种类</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">容量</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t xml:space="preserve">单价</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用工人数</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">年产能</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">电芯产线</t>
+          <t xml:space="preserve">原料仓</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400000</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>120</v>
+          <t xml:space="preserve">MATERIAL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30000</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">400000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">电驱总装线</t>
+          <t xml:space="preserve">零件仓</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600000</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>80</v>
+          <t xml:space="preserve">PART</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20000</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">300000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">车身冲压线</t>
+          <t xml:space="preserve">整车成品仓</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200000</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>60</v>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8000</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9000</t>
+          <t xml:space="preserve">600000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">整车总装线</t>
+          <t xml:space="preserve">燃料储罐</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3600000</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>200</v>
+          <t xml:space="preserve">FUEL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10000</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">200000</t>
         </is>
       </c>
     </row>
@@ -1091,142 +1081,97 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建名称</t>
+          <t xml:space="preserve">零件名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">占地面积</t>
+          <t xml:space="preserve">原料配比</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">启用费用</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">就业率加成</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">人口加成</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高素质人口加成</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">幸福度加成</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">人均收益加成</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">减碳加成</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">智能充电站</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>80</v>
+          <t xml:space="preserve">动力电池包</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">锂矿石*4; 铝土矿*1</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">600000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.01</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.04</t>
+          <t xml:space="preserve">电池成组技术</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">汽车试验场</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>200</v>
+          <t xml:space="preserve">驱动电机</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">铁矿石*2; 铝土矿*2</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1500000</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80000</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.03</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.02</t>
+          <t xml:space="preserve">电驱系统集成</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">光伏电站</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>160</v>
+          <t xml:space="preserve">铝合金车身</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">铝土矿*4; 铁矿石*1</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200000</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50000</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.02</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.12</t>
+          <t xml:space="preserve">轻量化车身工艺</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汽车轮胎</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天然橡胶*3; 铁矿石*1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">智能座舱域控</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">石英砂*3; 铝土矿*1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">电驱系统集成</t>
         </is>
       </c>
     </row>
@@ -1240,110 +1185,68 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库名称</t>
+          <t xml:space="preserve">产品名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库种类</t>
+          <t xml:space="preserve">零件配比</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">容量</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料仓</t>
+          <t xml:space="preserve">纯电轿车</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATERIAL</t>
+          <t xml:space="preserve">动力电池包*1; 驱动电机*1; 铝合金车身*1; 汽车轮胎*4; 智能座舱域控*1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400000</t>
+          <t xml:space="preserve">整车平台化</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件仓</t>
+          <t xml:space="preserve">纯电SUV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PART</t>
+          <t xml:space="preserve">动力电池包*1; 驱动电机*2; 铝合金车身*1; 汽车轮胎*4; 智能座舱域控*1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20000</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300000</t>
+          <t xml:space="preserve">整车平台化</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">整车成品仓</t>
+          <t xml:space="preserve">商用电动轻卡</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">动力电池包*2; 驱动电机*2; 铝合金车身*1; 汽车轮胎*6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">600000</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">燃料储罐</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FUEL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10000</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200000</t>
+          <t xml:space="preserve">整车平台化</t>
         </is>
       </c>
     </row>
@@ -1357,97 +1260,247 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件名称</t>
+          <t xml:space="preserve">载具名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料配比</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">所需科技</t>
+          <t xml:space="preserve">可通行路径类型</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每公里油耗</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载货量</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单价</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">动力电池包</t>
+          <t xml:space="preserve">矿用自卸车</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">锂矿石*4; 铝土矿*1</t>
+          <t xml:space="preserve">柴油</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">电池成组技术</t>
+          <t xml:space="preserve">公路</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.45</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>60</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">驱动电机</t>
+          <t xml:space="preserve">重型卡车</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">铁矿石*2; 铝土矿*2</t>
+          <t xml:space="preserve">柴油</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">电驱系统集成</t>
+          <t xml:space="preserve">公路</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.35</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">铝合金车身</t>
+          <t xml:space="preserve">商品车运输车</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">铝土矿*4; 铁矿石*1</t>
+          <t xml:space="preserve">柴油</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">轻量化车身工艺</t>
+          <t xml:space="preserve">公路</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.42</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">汽车轮胎</t>
+          <t xml:space="preserve">电动重卡</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">天然橡胶*3; 铁矿石*1</t>
+          <t xml:space="preserve">电力</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公路</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.2</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>25</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">智能座舱域控</t>
+          <t xml:space="preserve">货运列车</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">石英砂*3; 铝土矿*1</t>
+          <t xml:space="preserve">电力</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">电驱系统集成</t>
+          <t xml:space="preserve">铁路</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.05</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>800</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3200000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内河滚装船</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">柴油</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内河航运</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.06</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>1500</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5200000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
     </row>
@@ -1507,68 +1560,102 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">区域名称</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t xml:space="preserve">产品名称</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">零件配比</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">所需科技</t>
+          <t xml:space="preserve">需求量</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">备注</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">东部车都</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">纯电轿车</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">动力电池包*1; 驱动电机*1; 铝合金车身*1; 汽车轮胎*4; 智能座舱域控*1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">整车平台化</t>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">城市通勤主力车型</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t xml:space="preserve">东部车都</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t xml:space="preserve">纯电SUV</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">动力电池包*1; 驱动电机*2; 铝合金车身*1; 汽车轮胎*4; 智能座舱域控*1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">整车平台化</t>
+      <c r="C3">
+        <v>600</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">家庭用车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">中部智造区</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t xml:space="preserve">商用电动轻卡</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">动力电池包*2; 驱动电机*2; 铝合金车身*1; 汽车轮胎*6</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">整车平台化</t>
+      <c r="C4">
+        <v>300</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">园区物流用车</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上游资源区</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商用电动轻卡</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>120</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矿区自用与通勤</t>
         </is>
       </c>
     </row>
@@ -1582,1100 +1669,113 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具名称</t>
+          <t xml:space="preserve">类型标识</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">合同名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">可通行路径类型</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">每公里油耗</t>
+          <t xml:space="preserve">脚本路径</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">载货量</t>
+          <t xml:space="preserve">参与方</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">输入项定义</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">碳排系数</t>
+          <t xml:space="preserve">效果定义</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前置检查</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否启用</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿用自卸车</t>
+          <t xml:space="preserve">auto-mining</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">柴油</t>
+          <t xml:space="preserve">开采合同</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">公路</t>
+          <t xml:space="preserve">开采企业向矿区管理方缴纳权利金与环保费，扣减许可配额并把原矿入库</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.45</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>60</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900000</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.2</t>
+          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">重型卡车</t>
+          <t xml:space="preserve">auto-purchase-sale</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">柴油</t>
+          <t xml:space="preserve">购销合同</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">公路</t>
+          <t xml:space="preserve">按卖方所在地价结算货款，货物出库 / 入库并登记双方台账</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.35</t>
-        </is>
-      </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260000</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.9</t>
+          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品车运输车</t>
+          <t xml:space="preserve">auto-transport</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">柴油</t>
+          <t xml:space="preserve">运输合同</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">公路</t>
+          <t xml:space="preserve">按最短路径路程与载具计费，超重加价，里程与碳排计入台账</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.42</t>
-        </is>
-      </c>
-      <c r="E4">
-        <v>12</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">480000</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">电动重卡</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">电力</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公路</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.2</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>25</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">620000</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">货运列车</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">电力</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">铁路</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.05</t>
-        </is>
-      </c>
-      <c r="E6">
-        <v>800</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3200000</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内河滚装船</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">柴油</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内河航运</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.06</t>
-        </is>
-      </c>
-      <c r="E7">
-        <v>1500</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5200000</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">区域名称</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">产品名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">需求量</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">纯电轿车</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>1200</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">城市通勤主力车型</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">纯电SUV</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>600</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">家庭用车</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造区</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">商用电动轻卡</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>300</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">园区物流用车</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">商用电动轻卡</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>120</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">矿区自用与通勤</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">区域名称</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公司名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">字段键</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">卡片标题</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">分区标记</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">卡片ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cash</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业现金</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inventory</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业库存</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">戈壁铝业</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cash</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">戈壁铝业现金</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造区</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中原创能</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cash</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中原创能现金</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造区</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中原创能</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inventory</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中原创能库存</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造区</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">智造电驱</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cash</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">智造电驱现金</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">车都新能源</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cash</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">车都新能源现金</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">车都新能源</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inventory</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">车都新能源库存</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东都汽车销售</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cash</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东都汽车销售现金</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">类型标识</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">说明</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">脚本路径</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参与方</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输入项定义</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">效果定义</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前置检查</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否启用</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto-mining</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开采合同</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开采企业向矿区管理方缴纳权利金与环保费，扣减许可配额并把原矿入库</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
           <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto-purchase-sale</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">购销合同</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">按卖方所在地价结算货款，货物出库 / 入库并登记双方台账</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto-transport</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">运输合同</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">按最短路径路程与载具计费，超重加价，里程与碳排计入台账</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型标识</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参与方</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输入项</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto-mining</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开采合同</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">miner=西岭锂业|MIN-2026-001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ore_type=锂矿石; quantity=20; royalty_rate=60; env_fee_rate=8; carbon_factor=0.5</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DRAFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto-purchase-sale</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">购销合同</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">seller=西岭锂业|SL-2026-001; buyer=中原创能|BY-2026-001</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goods={"锂矿石": 20}; discount=0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DRAFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto-transport</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">运输合同</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">client=中原创能|PL-2026-001; carrier=车都新能源|TR-2026-001</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rate_per_km=12; trips=1; cargo_weight=20; carbon_tax_rate=0.05; vehicles={"重型卡车": 2}</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DRAFT</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">标题</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">正文</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否发给全体</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">指定收件人</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发布者</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开局公告</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">欢迎参加 2026 汽车产业链测试赛。本场共三大产业：上游「原料开采」、中游「零部件加工」、下游「整车进销」。请先在「公司管理」核对本公司初始字段，再到「合同管理」查看三份待签合同（开采 / 购销 / 运输）。</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">产业链玩法说明</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">① 开采企业用「开采合同」缴纳权利金与环保费取得原矿（扣减许可配额）；\n② 用「运输合同」把原矿从矿区运到中部智造园（按最短路径计费，超重加价）；\n③ 用「购销合同」把原料卖给加工企业，加工企业按零件配比生产零部件；\n④ 再用「运输合同」把零部件运到东部车都，用「购销合同」卖给整车企业；\n⑤ 整车企业按产品配比总装整车，交付东部车都的消费者需求。</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">裁判提示</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同执行金额请保留两位小数；提交前可用合同详情里的「试算」核对落账。</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用户名</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">角色</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">显示名</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公司管理范围</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">查看范围</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同查看范围</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">股票范围</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">权限键</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否启用</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto_player_a</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLAYER</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">玩家A（锂电链）</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业; 中原创能; 车都新能源</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业; 中原创能; 车都新能源</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业; 中原创能; 车都新能源</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto_player_b</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLAYER</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">玩家B（铝驱链）</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">戈壁铝业; 智造电驱; 东都汽车销售</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">戈壁铝业; 智造电驱; 东都汽车销售</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">戈壁铝业; 智造电驱; 东都汽车销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto_player_c</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLAYER</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">玩家C（铁矿车身链）</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白云矿业; 轻量化车身厂; 车都出口贸易</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白云矿业; 轻量化车身厂; 车都出口贸易</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白云矿业; 轻量化车身厂; 车都出口贸易</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto_referee</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COMPETITION_ADMIN</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">本场裁判</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业; 戈壁铝业; 白云矿业; 中原创能; 智造电驱; 轻量化车身厂; 车都新能源; 东都汽车销售; 车都出口贸易</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业; 戈壁铝业; 白云矿业; 中原创能; 智造电驱; 轻量化车身厂; 车都新能源; 东都汽车销售; 车都出口贸易</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业; 戈壁铝业; 白云矿业; 中原创能; 智造电驱; 轻量化车身厂; 车都新能源; 东都汽车销售; 车都出口贸易</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">contract:manage; contract:audit; contract:execute</t>
         </is>
       </c>
     </row>
@@ -4387,470 +3487,85 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司名称</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属产业</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属区域</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">状态</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">所在地</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">现金</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">银行存款</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">许可配额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">库存台账</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">西岭锂业</t>
+          <t xml:space="preserve">矿区</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料开采</t>
+          <t xml:space="preserve">原矿开采地</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTIVE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白云鄂博矿区</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1200000</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"原矿": 120, "锂矿石": 40}</t>
+          <t xml:space="preserve">#b45309</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">戈壁铝业</t>
+          <t xml:space="preserve">产业园区</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料开采</t>
+          <t xml:space="preserve">加工制造基地</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTIVE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">戈壁铝土矿区</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900000</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200000</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">600</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"原矿": 80, "铝土矿": 30}</t>
+          <t xml:space="preserve">#2563eb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">白云矿业</t>
+          <t xml:space="preserve">物流枢纽</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料开采</t>
+          <t xml:space="preserve">集运站 / 港口 / 铁路货场</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTIVE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白云鄂博矿区</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800000</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150000</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">500</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"原矿": 60, "铁矿石": 25}</t>
+          <t xml:space="preserve">#0ea5e9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">中原创能</t>
+          <t xml:space="preserve">销售中心</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">零部件加工</t>
+          <t xml:space="preserve">整车展销与交付中心</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">中部智造区</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTIVE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造园</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1500000</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">500000</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">600</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"货物": 60, "锂矿石": 20}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">智造电驱</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">零部件加工</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造区</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTIVE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造园</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1200000</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400000</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">500</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"货物": 45}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">轻量化车身厂</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">零部件加工</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中部智造区</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTIVE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中原铁路货场</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000000</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300000</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"货物": 30}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">车都新能源</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">整车进销</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTIVE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都港</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000000</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000000</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"货物": 40, "零件": 20}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东都汽车销售</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">整车进销</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTIVE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">车都展销中心</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2000000</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800000</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"货物": 25}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">车都出口贸易</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">整车进销</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTIVE</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都港</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1800000</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">600000</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"货物": 18}</t>
+          <t xml:space="preserve">#7c3aed</t>
         </is>
       </c>
     </row>
@@ -4864,68 +3579,68 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司名称</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段键</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">值</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">西岭锂业</t>
+          <t xml:space="preserve">公路</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">最近业务摘要</t>
+          <t xml:space="preserve">通用公路运输</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">开局初始化</t>
+          <t xml:space="preserve">#94a3b8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">中原创能</t>
+          <t xml:space="preserve">铁路</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">业务台账</t>
+          <t xml:space="preserve">大宗干线运输</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"开局盘点": 1}</t>
+          <t xml:space="preserve">#a16207</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">车都新能源</t>
+          <t xml:space="preserve">内河航运</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">业务台账</t>
+          <t xml:space="preserve">港口水运</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"开局盘点": 1}</t>
+          <t xml:space="preserve">#0369a1</t>
         </is>
       </c>
     </row>
@@ -4939,86 +3654,212 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型名称</t>
+          <t xml:space="preserve">节点名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">节点类型</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">颜色</t>
+          <t xml:space="preserve">所属区域</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X坐标</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y坐标</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">白云鄂博矿区</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">矿区</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">原矿开采地</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#b45309</t>
-        </is>
+          <t xml:space="preserve">上游资源区</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>140</v>
+      </c>
+      <c r="E2">
+        <v>120</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业园区</t>
+          <t xml:space="preserve">戈壁铝土矿区</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">加工制造基地</t>
+          <t xml:space="preserve">矿区</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2563eb</t>
-        </is>
+          <t xml:space="preserve">上游资源区</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>140</v>
+      </c>
+      <c r="E3">
+        <v>300</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">物流枢纽</t>
+          <t xml:space="preserve">橡胶硅砂基地</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">集运站 / 港口 / 铁路货场</t>
+          <t xml:space="preserve">矿区</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">#0ea5e9</t>
-        </is>
+          <t xml:space="preserve">上游资源区</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>140</v>
+      </c>
+      <c r="E4">
+        <v>480</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t xml:space="preserve">上游集运站</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物流枢纽</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上游资源区</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>360</v>
+      </c>
+      <c r="E5">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中部智造园</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业园区</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中部智造区</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>620</v>
+      </c>
+      <c r="E6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中原铁路货场</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物流枢纽</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中部智造区</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>620</v>
+      </c>
+      <c r="E7">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东部车都港</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物流枢纽</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东部车都</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>900</v>
+      </c>
+      <c r="E8">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">车都展销中心</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t xml:space="preserve">销售中心</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">整车展销与交付中心</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#7c3aed</t>
-        </is>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东部车都</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>1040</v>
+      </c>
+      <c r="E9">
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/backend/examples/excel/汽车产业链示例.xlsx
+++ b/backend/examples/excel/汽车产业链示例.xlsx
@@ -1669,45 +1669,15 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">脚本路径</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t xml:space="preserve">类型标识</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同名称</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">说明</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">脚本路径</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参与方</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输入项定义</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">效果定义</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前置检查</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">是否启用</t>
         </is>
@@ -1716,66 +1686,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">auto-mining</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开采合同</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">开采企业向矿区管理方缴纳权利金与环保费，扣减许可配额并把原矿入库</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t xml:space="preserve">auto-purchase-sale</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">购销合同</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">按卖方所在地价结算货款，货物出库 / 入库并登记双方台账</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t xml:space="preserve">auto-transport</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">运输合同</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">按最短路径路程与载具计费，超重加价，里程与碳排计入台账</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
